--- a/artfynd/A 24772-2026 artfynd.xlsx
+++ b/artfynd/A 24772-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545996</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545993</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545992</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545998</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545230</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545985</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545987</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546149</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546151</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546154</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546158</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1981,6 +2041,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546159</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546160</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546161</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546169</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546170</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2551,6 +2636,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545228</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2673,6 +2763,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545226</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2780,6 +2875,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545229</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2887,6 +2987,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545231</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2994,6 +3099,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545234</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3101,6 +3211,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545235</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3208,6 +3323,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545237</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3315,6 +3435,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545988</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3422,6 +3547,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545994</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3529,6 +3659,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545999</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3636,6 +3771,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546002</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3743,6 +3883,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546162</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3850,6 +3995,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546163</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3957,6 +4107,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546167</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4064,6 +4219,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545997</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4171,6 +4331,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545232</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4278,6 +4443,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545991</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4385,6 +4555,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545227</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4492,6 +4667,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545984</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4599,6 +4779,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546000</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4706,6 +4891,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546001</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4828,6 +5018,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545238</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4935,6 +5130,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545990</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5042,6 +5242,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545995</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5149,6 +5354,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546004</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5271,6 +5481,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545239</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5396,6 +5611,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545233</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5508,6 +5728,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546003</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5620,6 +5845,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546148</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5732,6 +5962,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546150</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5844,6 +6079,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546152</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5956,6 +6196,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546153</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6068,6 +6313,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546155</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6180,6 +6430,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546157</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6292,6 +6547,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546164</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6404,6 +6664,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546166</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6516,6 +6781,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546168</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6628,6 +6898,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546171</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6740,6 +7015,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546172</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6852,6 +7132,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546173</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6964,6 +7249,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546174</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7076,6 +7366,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546175</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7188,6 +7483,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546176</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7295,6 +7595,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134546165</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7402,6 +7707,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545236</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7509,6 +7819,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545986</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7616,8 +7931,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134545989</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>